--- a/MainTop/29.05.2026 Макс Имена/print_test.xlsx
+++ b/MainTop/29.05.2026 Макс Имена/print_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\29.05.2026 Макс Имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305E1614-3572-4741-A960-D36A0F42FB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EF1AC8-AD48-4E18-8A43-4DC4DD08C7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,7 +471,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -486,7 +486,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -501,7 +501,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -516,7 +516,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
